--- a/tests/fixtures/maple-plaza/client.xlsx
+++ b/tests/fixtures/maple-plaza/client.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
   <si>
     <t>Maple Plaza — Rent Roll</t>
   </si>
@@ -44,6 +44,9 @@
   </si>
   <si>
     <t>Rent Steps</t>
+  </si>
+  <si>
+    <t>% Rent</t>
   </si>
   <si>
     <t>100</t>
@@ -480,10 +483,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -508,8 +511,11 @@
       <c r="H1" t="s">
         <v>1</v>
       </c>
+      <c r="I1" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -534,8 +540,11 @@
       <c r="H2" t="s">
         <v>1</v>
       </c>
+      <c r="I2" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -560,108 +569,123 @@
       <c r="H4" t="s">
         <v>10</v>
       </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>54408</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>41940</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
       </c>
+      <c r="I5" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6">
         <v>3000</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>90000</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
+        <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>10040</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7">
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H7" t="s">
         <v>1</v>
       </c>
+      <c r="I7" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8">
         <v>2500</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F8">
         <v>100000</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
         <v>1</v>
       </c>
     </row>
